--- a/assets/docs/lop4/Toan - Lop 4.xlsx
+++ b/assets/docs/lop4/Toan - Lop 4.xlsx
@@ -1668,19 +1668,19 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Một số đơn vị đo đại lượng</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Yến, tạ, tấn (Tiết 1)</t>
+          <t>Kiểm tra định kì giữa học kì I</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -1688,11 +1688,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
-        </is>
-      </c>
+      <c r="H40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1709,10 +1705,14 @@
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Yến, tạ, tấn (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
+          <t>Bài 17. Yến, tạ, tấn (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>38</t>
@@ -1739,7 +1739,7 @@
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Yến, tạ, tấn (Tiết 3)</t>
+          <t>Bài 17. Yến, tạ, tấn (Tiết 2)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.4 CB2a: HS tự soát lại bài bằng công cụ chấm nhanh của GV và chỉ ra dạng quy đổi mình còn hay nhầm.</t>
+          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
         </is>
       </c>
     </row>
@@ -1769,14 +1769,10 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>4 tiết</t>
-        </is>
-      </c>
+          <t>Bài 17. Yến, tạ, tấn (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr">
         <is>
           <t>40</t>
@@ -1784,7 +1780,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
+          <t>Năng lực số 5.4 CB2a: HS tự soát lại bài bằng công cụ chấm nhanh của GV và chỉ ra dạng quy đổi mình còn hay nhầm.</t>
         </is>
       </c>
     </row>
@@ -1803,10 +1799,14 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>4 tiết</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>41</t>
@@ -1833,7 +1833,7 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 3)</t>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 2)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 4)</t>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 3)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -1893,14 +1893,10 @@
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Giây, thế kỉ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 4)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
           <t>44</t>
@@ -1908,8 +1904,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.
-STEM: Thế kỉ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
+          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
         </is>
       </c>
     </row>
@@ -1928,10 +1923,14 @@
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Giây, thế kỉ (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
+          <t>Bài 19. Giây, thế kỉ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>45</t>
@@ -1939,7 +1938,8 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
+          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.
+STEM: Thế kỉ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1951,21 +1951,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 4: Một số đơn vị đo đại lượng</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 19. Giây, thế kỉ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
           <t>46</t>
@@ -2316,11 +2312,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2346,11 +2338,7 @@
           <t>58</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB2a: HS làm bài tập tương tác, tự xác định dạng bài mình còn yếu và luyện thêm.</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2633,11 +2621,7 @@
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2762,11 +2746,7 @@
           <t>71</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3074,11 +3054,7 @@
           <t>81</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -3104,11 +3080,7 @@
           <t>82</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -3875,11 +3847,7 @@
           <t>107</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
-        </is>
-      </c>
+      <c r="H110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -3905,11 +3873,7 @@
           <t>108</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
-        </is>
-      </c>
+      <c r="H111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -4707,11 +4671,7 @@
           <t>133</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS giải thích được khái niệm phân số và phân số bằng nhau nhờ quan sát mô hình động.</t>
-        </is>
-      </c>
+      <c r="H136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -4741,11 +4701,7 @@
           <t>134</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS giải thích được khái niệm phân số và phân số bằng nhau nhờ quan sát mô hình động.</t>
-        </is>
-      </c>
+      <c r="H137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -5104,11 +5060,7 @@
           <t>146</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB2a: HS làm bài tập tương tác, tự xác định dạng bài mình còn yếu và luyện thêm.</t>
-        </is>
-      </c>
+      <c r="H149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -5658,11 +5610,7 @@
           <t>164</t>
         </is>
       </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc, viết, so sánh, làm tròn được các số lớn lấy từ số liệu thật, có ghi nguồn.</t>
-        </is>
-      </c>
+      <c r="H167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -5688,11 +5636,7 @@
           <t>165</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc, viết, so sánh, làm tròn được các số lớn lấy từ số liệu thật, có ghi nguồn.</t>
-        </is>
-      </c>
+      <c r="H168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -5786,11 +5730,7 @@
           <t>168</t>
         </is>
       </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS giải thích được khái niệm phân số và phân số bằng nhau nhờ quan sát mô hình động.</t>
-        </is>
-      </c>
+      <c r="H171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
